--- a/data/trans_dic/P37A$vacunapreferencia-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunapreferencia-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,69</t>
+          <t>0,87; 4,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,84</t>
+          <t>2,26; 7,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,82</t>
+          <t>1,02; 4,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,21</t>
+          <t>4,13; 9,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,63</t>
+          <t>1,19; 5,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,54</t>
+          <t>2,75; 8,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,57</t>
+          <t>4,74; 9,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,2</t>
+          <t>1,44; 4,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,27</t>
+          <t>1,33; 3,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,57</t>
+          <t>2,33; 5,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,55</t>
+          <t>5,02; 8,47</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,45</t>
+          <t>1,91; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,21</t>
+          <t>1,42; 4,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,32</t>
+          <t>0,41; 2,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,7</t>
+          <t>6,29; 11,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,05</t>
+          <t>0,74; 2,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,76</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,77</t>
+          <t>1,08; 3,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,66</t>
+          <t>4,88; 8,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,55</t>
+          <t>1,49; 3,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,47</t>
+          <t>1,0; 2,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,7</t>
+          <t>0,95; 2,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,64</t>
+          <t>6,06; 9,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,85</t>
+          <t>1,45; 5,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,56</t>
+          <t>1,81; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,54</t>
+          <t>0,87; 4,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,27</t>
+          <t>1,68; 4,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,69</t>
+          <t>0,57; 3,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,61</t>
+          <t>0,29; 2,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,91</t>
+          <t>0,61; 4,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,8</t>
+          <t>2,57; 6,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,5</t>
+          <t>1,17; 3,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,99</t>
+          <t>1,32; 3,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,53</t>
+          <t>1,11; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,76</t>
+          <t>2,45; 4,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,77</t>
+          <t>1,26; 5,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,19</t>
+          <t>1,99; 6,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,75</t>
+          <t>0,48; 2,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,83</t>
+          <t>2,67; 7,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,87</t>
+          <t>1,0; 3,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,56</t>
+          <t>1,75; 5,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,01</t>
+          <t>4,98; 9,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,59</t>
+          <t>1,4; 3,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,1</t>
+          <t>2,3; 5,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,79</t>
+          <t>0,38; 1,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,18</t>
+          <t>4,37; 7,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 8,11</t>
+          <t>2,19; 7,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,49</t>
+          <t>0,97; 5,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,03</t>
+          <t>1,31; 6,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,12</t>
+          <t>6,1; 12,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,69</t>
+          <t>1,3; 7,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,03</t>
+          <t>0,89; 5,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,33</t>
+          <t>6,46; 11,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,57</t>
+          <t>2,41; 6,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,9</t>
+          <t>0,94; 3,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,39</t>
+          <t>1,41; 4,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,28</t>
+          <t>7,1; 10,96</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,32</t>
+          <t>1,01; 4,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,23</t>
+          <t>1,43; 5,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,68</t>
+          <t>1,33; 6,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,39</t>
+          <t>0,68; 3,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,31</t>
+          <t>1,18; 5,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,59</t>
+          <t>2,15; 7,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,26</t>
+          <t>1,8; 6,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,21</t>
+          <t>1,22; 4,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,84</t>
+          <t>1,28; 3,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,18</t>
+          <t>2,11; 5,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,99</t>
+          <t>1,83; 4,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,35</t>
+          <t>1,2; 3,45</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,6</t>
+          <t>1,8; 4,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,78</t>
+          <t>2,53; 5,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,89</t>
+          <t>0,18; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,24</t>
+          <t>6,49; 10,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,06</t>
+          <t>2,11; 5,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,31</t>
+          <t>1,72; 4,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,19</t>
+          <t>0,43; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,87</t>
+          <t>6,01; 9,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,29</t>
+          <t>2,22; 4,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,44</t>
+          <t>2,42; 4,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,6</t>
+          <t>0,45; 1,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 8,71</t>
+          <t>6,86; 9,79</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,89</t>
+          <t>1,51; 3,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,91</t>
+          <t>0,94; 2,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,54</t>
+          <t>0,73; 2,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,01</t>
+          <t>10,5; 15,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,18</t>
+          <t>1,63; 3,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,83</t>
+          <t>0,87; 2,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,98</t>
+          <t>0,5; 2,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,79</t>
+          <t>10,73; 14,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,52</t>
+          <t>1,77; 3,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,65</t>
+          <t>1,12; 2,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,86</t>
+          <t>0,79; 1,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,42</t>
+          <t>11,2; 14,17</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,45</t>
+          <t>2,24; 3,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,69</t>
+          <t>2,45; 3,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,15</t>
+          <t>1,22; 2,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,33</t>
+          <t>6,96; 8,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,2</t>
+          <t>2,06; 3,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,49</t>
+          <t>1,49; 2,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,33</t>
+          <t>1,38; 2,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,0</t>
+          <t>7,14; 8,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,09</t>
+          <t>2,29; 3,11</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,85</t>
+          <t>2,1; 2,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,42; 2,05</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,96</t>
+          <t>7,29; 8,48</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>41788</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2346; 12791</t>
+          <t>2386; 12859</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7225; 23118</t>
+          <t>6655; 22117</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2835; 14159</t>
+          <t>3008; 13334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13656; 34923</t>
+          <t>13162; 30760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3069; 14684</t>
+          <t>3115; 15482</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>0; 4779</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8071; 24652</t>
+          <t>7942; 24392</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15434; 30628</t>
+          <t>14990; 29202</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6986; 22437</t>
+          <t>7678; 22596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8304; 24875</t>
+          <t>7716; 22472</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13001; 32447</t>
+          <t>13563; 32716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33881; 57430</t>
+          <t>31881; 53771</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44280</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>36028</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79221</t>
+          <t>81505</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8753; 26887</t>
+          <t>9420; 29346</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7001; 21274</t>
+          <t>7197; 22418</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2005; 11661</t>
+          <t>2068; 11876</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31270; 60628</t>
+          <t>33392; 61813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3814; 15351</t>
+          <t>3745; 14884</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1015; 9241</t>
+          <t>964; 9210</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5964; 19724</t>
+          <t>5648; 19625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25663; 44578</t>
+          <t>26647; 47250</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14044; 35393</t>
+          <t>14845; 35785</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10011; 25379</t>
+          <t>10315; 26226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9931; 27665</t>
+          <t>9787; 26659</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>63518; 99661</t>
+          <t>65295; 102020</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>24065</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3931; 15463</t>
+          <t>4615; 16082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5865; 21272</t>
+          <t>5881; 22141</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3227; 14452</t>
+          <t>2783; 15186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5591; 16649</t>
+          <t>5296; 15684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1919; 12362</t>
+          <t>1901; 12671</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>978; 8889</t>
+          <t>972; 8979</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2155; 13140</t>
+          <t>2039; 13881</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8159; 20245</t>
+          <t>9170; 22541</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7690; 22884</t>
+          <t>7646; 22469</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8735; 26543</t>
+          <t>8806; 25788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6999; 23142</t>
+          <t>7263; 22528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16032; 31662</t>
+          <t>16444; 33137</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>28980</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>45792</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3844; 17116</t>
+          <t>4510; 18050</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6473; 23152</t>
+          <t>7434; 23233</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1006; 10163</t>
+          <t>1779; 10084</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8855; 24473</t>
+          <t>9950; 27393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3555; 14368</t>
+          <t>3713; 14732</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7102; 21615</t>
+          <t>6800; 20122</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5698</t>
+          <t>0; 6429</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15005; 38082</t>
+          <t>21030; 39679</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10269; 26188</t>
+          <t>10228; 26089</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17614; 38934</t>
+          <t>17521; 39744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2825; 13563</t>
+          <t>2845; 12536</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28055; 56599</t>
+          <t>34753; 59280</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>38388</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4571; 16495</t>
+          <t>4452; 15781</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2136; 13804</t>
+          <t>2063; 12511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2646; 12734</t>
+          <t>2764; 14013</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11371; 23457</t>
+          <t>12541; 25044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2902; 15970</t>
+          <t>2708; 15785</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6375</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1936; 10997</t>
+          <t>1952; 12061</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10635; 26735</t>
+          <t>14788; 26139</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9747; 27004</t>
+          <t>9889; 25717</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4096; 16854</t>
+          <t>4064; 16786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6191; 18884</t>
+          <t>6059; 20078</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23306; 44986</t>
+          <t>30861; 47634</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>11208</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1977; 11707</t>
+          <t>2744; 11678</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3098; 14330</t>
+          <t>3905; 15406</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3079; 14956</t>
+          <t>3504; 15915</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2188; 11840</t>
+          <t>1852; 10633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3054; 14768</t>
+          <t>3285; 14278</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5125; 18468</t>
+          <t>6025; 19823</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4194; 17101</t>
+          <t>4913; 18015</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3022; 10818</t>
+          <t>3213; 10659</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6904; 21063</t>
+          <t>7048; 21165</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11762; 28689</t>
+          <t>11715; 28032</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9907; 26760</t>
+          <t>9830; 26618</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6179; 17628</t>
+          <t>6436; 18452</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49803</t>
+          <t>61804</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>52715</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>102518</t>
+          <t>121484</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11480; 28268</t>
+          <t>11100; 28248</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16508; 38313</t>
+          <t>16748; 36928</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1191; 12432</t>
+          <t>1174; 14210</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35964; 63947</t>
+          <t>46725; 78559</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13769; 32321</t>
+          <t>13454; 34539</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12033; 29929</t>
+          <t>11934; 30461</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3056; 15136</t>
+          <t>3001; 16189</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26489; 75372</t>
+          <t>46393; 74765</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28559; 53822</t>
+          <t>27829; 53943</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32653; 60288</t>
+          <t>32828; 59435</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6389; 21546</t>
+          <t>6023; 22296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>63393; 128391</t>
+          <t>102280; 146109</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88947</t>
+          <t>100529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>106065</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>179103</t>
+          <t>206594</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10565; 28925</t>
+          <t>11240; 29346</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8085; 22659</t>
+          <t>7292; 22702</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5477; 19748</t>
+          <t>5691; 18252</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38257; 130156</t>
+          <t>83785; 120623</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13840; 32761</t>
+          <t>12767; 31276</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6652; 23310</t>
+          <t>7129; 24011</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4128; 16366</t>
+          <t>4119; 16738</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>76855; 106128</t>
+          <t>89185; 123057</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28410; 53774</t>
+          <t>26974; 53451</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>17960; 42553</t>
+          <t>17885; 38810</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12484; 29780</t>
+          <t>12701; 29855</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>114104; 221027</t>
+          <t>182509; 230930</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>251852</t>
+          <t>277278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>265094</t>
+          <t>293546</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>516946</t>
+          <t>570824</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>74819; 113119</t>
+          <t>73364; 111372</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>86116; 126484</t>
+          <t>83812; 125526</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42595; 73043</t>
+          <t>41274; 70793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>199770; 288312</t>
+          <t>245821; 310395</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>67545; 108075</t>
+          <t>69680; 105793</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>53628; 88684</t>
+          <t>52958; 85022</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49125; 82588</t>
+          <t>48741; 82379</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>211722; 296987</t>
+          <t>266758; 325441</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>151285; 205842</t>
+          <t>152147; 207189</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147335; 199000</t>
+          <t>146471; 200010</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98108; 143223</t>
+          <t>98580; 142538</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>448678; 571131</t>
+          <t>530256; 616274</t>
         </is>
       </c>
     </row>
